--- a/Result/profitability/4711.xlsx
+++ b/Result/profitability/4711.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08499999999999999</v>
+        <v>0.14875</v>
       </c>
       <c r="N2" t="n">
-        <v>12.21375</v>
+        <v>13.7375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.66</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1725</v>
+        <v>0.22125</v>
       </c>
       <c r="N3" t="n">
-        <v>12.28125</v>
+        <v>13.56125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2</v>
+        <v>0.2575</v>
       </c>
       <c r="N4" t="n">
-        <v>11.7225</v>
+        <v>13.28875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.19375</v>
+        <v>0.2525</v>
       </c>
       <c r="N5" t="n">
-        <v>10.7475</v>
+        <v>12.16</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>0.245</v>
+        <v>0.29</v>
       </c>
       <c r="N6" t="n">
-        <v>11.025</v>
+        <v>12.22875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0.31</v>
+        <v>0.36375</v>
       </c>
       <c r="N7" t="n">
-        <v>11.32125</v>
+        <v>12.29</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.375</v>
+        <v>0.405</v>
       </c>
       <c r="N8" t="n">
-        <v>10.91625</v>
+        <v>11.3775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.84</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4675</v>
+        <v>0.4674999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>10.20125</v>
@@ -9832,6 +9832,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4711</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>244</v>
+      </c>
+      <c r="D75" t="n">
+        <v>190</v>
+      </c>
+      <c r="E75" t="n">
+        <v>55</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="G75" t="n">
+        <v>34</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>35</v>
+      </c>
+      <c r="K75" t="n">
+        <v>29</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.94375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.689999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1976432779860737</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.021699819168174</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
